--- a/Tools/Luban/DataTables/Datas/Item.xlsx
+++ b/Tools/Luban/DataTables/Datas/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0893B91-11C6-A74E-9B58-903BC61CACAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5028A23-9B0B-ED46-B414-2D095B5890F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$D$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$E$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -187,6 +187,12 @@
   </si>
   <si>
     <t>test</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>Res/UI/item/Test</t>
   </si>
 </sst>
 </file>
@@ -642,17 +648,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="7"/>
     <col min="2" max="2" width="43" style="7" customWidth="1"/>
-    <col min="3" max="3" width="46.1640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" style="6"/>
-    <col min="5" max="16384" width="12.1640625" style="7"/>
+    <col min="3" max="4" width="46.1640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="6"/>
+    <col min="6" max="16384" width="12.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -662,11 +668,14 @@
       <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -676,11 +685,14 @@
       <c r="C2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -690,11 +702,12 @@
       <c r="C3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="3">
         <v>10001</v>
@@ -702,232 +715,242 @@
       <c r="C4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="12"/>
-    </row>
-    <row r="19" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="4:4" s="11" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D20" s="12"/>
-    </row>
-    <row r="21" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="12"/>
-    </row>
-    <row r="22" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D22" s="12"/>
-    </row>
-    <row r="23" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="12"/>
-    </row>
-    <row r="24" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D24" s="12"/>
-    </row>
-    <row r="25" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="12"/>
-    </row>
-    <row r="26" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="12"/>
-    </row>
-    <row r="27" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="12"/>
-    </row>
-    <row r="28" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="12"/>
-    </row>
-    <row r="29" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D29" s="12"/>
-    </row>
-    <row r="30" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D30" s="12"/>
-    </row>
-    <row r="31" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D31" s="12"/>
-    </row>
-    <row r="32" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D32" s="12"/>
-    </row>
-    <row r="33" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D34" s="12"/>
-    </row>
-    <row r="35" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="12"/>
-    </row>
-    <row r="36" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D36" s="12"/>
-    </row>
-    <row r="37" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D37" s="12"/>
-    </row>
-    <row r="38" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20" spans="5:5" s="11" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E21" s="12"/>
+    </row>
+    <row r="22" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E22" s="12"/>
+    </row>
+    <row r="23" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="12"/>
+    </row>
+    <row r="24" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E29" s="12"/>
+    </row>
+    <row r="30" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="12"/>
+    </row>
+    <row r="31" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E31" s="12"/>
+    </row>
+    <row r="32" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E32" s="12"/>
+    </row>
+    <row r="33" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="12"/>
+    </row>
+    <row r="35" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E35" s="12"/>
+    </row>
+    <row r="36" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="12"/>
+    </row>
+    <row r="37" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E37" s="12"/>
+    </row>
+    <row r="38" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C38" s="13"/>
-      <c r="D38" s="12"/>
-    </row>
-    <row r="39" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="12"/>
-    </row>
-    <row r="40" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D40" s="12"/>
-    </row>
-    <row r="41" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D41" s="12"/>
-    </row>
-    <row r="42" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D42" s="12"/>
-    </row>
-    <row r="43" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D43" s="12"/>
-    </row>
-    <row r="44" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D44" s="12"/>
-    </row>
-    <row r="45" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D45" s="12"/>
-    </row>
-    <row r="46" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D46" s="12"/>
-    </row>
-    <row r="47" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D47" s="12"/>
-    </row>
-    <row r="48" spans="3:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D49" s="12"/>
-    </row>
-    <row r="50" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D50" s="12"/>
-    </row>
-    <row r="51" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D51" s="12"/>
-    </row>
-    <row r="52" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D52" s="12"/>
-    </row>
-    <row r="53" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D53" s="12"/>
-    </row>
-    <row r="54" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D54" s="12"/>
-    </row>
-    <row r="55" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D55" s="12"/>
-    </row>
-    <row r="56" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D56" s="12"/>
-    </row>
-    <row r="57" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D57" s="12"/>
-    </row>
-    <row r="58" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D58" s="12"/>
-    </row>
-    <row r="59" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D59" s="12"/>
-    </row>
-    <row r="60" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D60" s="12"/>
-    </row>
-    <row r="61" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D61" s="12"/>
-    </row>
-    <row r="62" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D62" s="12"/>
-    </row>
-    <row r="63" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D38" s="13"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E39" s="12"/>
+    </row>
+    <row r="40" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E40" s="12"/>
+    </row>
+    <row r="41" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="12"/>
+    </row>
+    <row r="42" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E42" s="12"/>
+    </row>
+    <row r="43" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="12"/>
+    </row>
+    <row r="44" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E44" s="12"/>
+    </row>
+    <row r="45" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E45" s="12"/>
+    </row>
+    <row r="46" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="12"/>
+    </row>
+    <row r="47" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E47" s="12"/>
+    </row>
+    <row r="48" spans="3:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E49" s="12"/>
+    </row>
+    <row r="50" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E50" s="12"/>
+    </row>
+    <row r="51" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E51" s="12"/>
+    </row>
+    <row r="52" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E52" s="12"/>
+    </row>
+    <row r="53" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E53" s="12"/>
+    </row>
+    <row r="54" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E54" s="12"/>
+    </row>
+    <row r="55" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E55" s="12"/>
+    </row>
+    <row r="56" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E56" s="12"/>
+    </row>
+    <row r="57" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E57" s="12"/>
+    </row>
+    <row r="58" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E58" s="12"/>
+    </row>
+    <row r="59" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E59" s="12"/>
+    </row>
+    <row r="60" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E60" s="12"/>
+    </row>
+    <row r="61" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E61" s="12"/>
+    </row>
+    <row r="62" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E62" s="12"/>
+    </row>
+    <row r="63" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="14"/>
       <c r="C65" s="12"/>
       <c r="D65" s="12"/>
-    </row>
-    <row r="66" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E65" s="12"/>
+    </row>
+    <row r="66" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="14"/>
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
-    </row>
-    <row r="67" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E66" s="12"/>
+    </row>
+    <row r="67" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="14"/>
       <c r="C67" s="12"/>
       <c r="D67" s="12"/>
-    </row>
-    <row r="68" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E67" s="12"/>
+    </row>
+    <row r="68" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="14"/>
       <c r="C68" s="12"/>
       <c r="D68" s="12"/>
-    </row>
-    <row r="69" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E68" s="12"/>
+    </row>
+    <row r="69" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="14"/>
       <c r="C69" s="12"/>
       <c r="D69" s="12"/>
-    </row>
-    <row r="70" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E69" s="12"/>
+    </row>
+    <row r="70" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="14"/>
       <c r="C70" s="12"/>
       <c r="D70" s="12"/>
-    </row>
-    <row r="71" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="E70" s="12"/>
+    </row>
+    <row r="71" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="81" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="82" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="83" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -944,494 +967,576 @@
     <row r="94" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="95" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="96" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D109" s="12"/>
-    </row>
-    <row r="110" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D110" s="12"/>
-    </row>
-    <row r="111" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D111" s="12"/>
-    </row>
-    <row r="112" spans="4:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D112" s="12"/>
-    </row>
-    <row r="113" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D113" s="12"/>
-    </row>
-    <row r="114" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D114" s="12"/>
-    </row>
-    <row r="115" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D115" s="12"/>
-    </row>
-    <row r="116" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D116" s="12"/>
-    </row>
-    <row r="117" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D117" s="12"/>
-    </row>
-    <row r="118" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D118" s="12"/>
-    </row>
-    <row r="119" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D119" s="12"/>
-    </row>
-    <row r="120" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D120" s="12"/>
-    </row>
-    <row r="121" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D121" s="12"/>
-    </row>
-    <row r="122" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D122" s="12"/>
-    </row>
-    <row r="123" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="98" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="99" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="104" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="105" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="106" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="107" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="109" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E109" s="12"/>
+    </row>
+    <row r="110" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E110" s="12"/>
+    </row>
+    <row r="111" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E111" s="12"/>
+    </row>
+    <row r="112" spans="5:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E112" s="12"/>
+    </row>
+    <row r="113" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E113" s="12"/>
+    </row>
+    <row r="114" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E114" s="12"/>
+    </row>
+    <row r="115" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E115" s="12"/>
+    </row>
+    <row r="116" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E116" s="12"/>
+    </row>
+    <row r="117" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E117" s="12"/>
+    </row>
+    <row r="118" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E118" s="12"/>
+    </row>
+    <row r="119" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E119" s="12"/>
+    </row>
+    <row r="120" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E120" s="12"/>
+    </row>
+    <row r="121" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E121" s="12"/>
+    </row>
+    <row r="122" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E122" s="12"/>
+    </row>
+    <row r="123" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="14"/>
       <c r="B123" s="14"/>
-      <c r="D123" s="12"/>
-    </row>
-    <row r="124" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E123" s="12"/>
+    </row>
+    <row r="124" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="14"/>
       <c r="B124" s="14"/>
-      <c r="D124" s="12"/>
-    </row>
-    <row r="125" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E124" s="12"/>
+    </row>
+    <row r="125" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="14"/>
       <c r="B125" s="14"/>
-      <c r="D125" s="12"/>
-    </row>
-    <row r="126" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E125" s="12"/>
+    </row>
+    <row r="126" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="14"/>
       <c r="B126" s="14"/>
-      <c r="D126" s="12"/>
-    </row>
-    <row r="127" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E126" s="12"/>
+    </row>
+    <row r="127" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="14"/>
       <c r="B127" s="14"/>
-      <c r="D127" s="12"/>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E127" s="12"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
       <c r="C128" s="10"/>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D128" s="10"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
       <c r="C129" s="10"/>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D129" s="10"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="9"/>
       <c r="B130" s="9"/>
       <c r="C130" s="10"/>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D130" s="10"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="9"/>
       <c r="B131" s="9"/>
       <c r="C131" s="10"/>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D131" s="10"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="9"/>
       <c r="B132" s="9"/>
       <c r="C132" s="10"/>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D132" s="10"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="9"/>
       <c r="B133" s="9"/>
       <c r="C133" s="10"/>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D133" s="10"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="9"/>
       <c r="B134" s="9"/>
       <c r="C134" s="10"/>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D134" s="10"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="9"/>
       <c r="B135" s="9"/>
       <c r="C135" s="10"/>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D135" s="10"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="9"/>
       <c r="B136" s="9"/>
       <c r="C136" s="10"/>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D136" s="10"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="9"/>
       <c r="B137" s="9"/>
       <c r="C137" s="10"/>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D137" s="10"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="9"/>
       <c r="B138" s="9"/>
       <c r="C138" s="10"/>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D138" s="10"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="9"/>
       <c r="B139" s="9"/>
       <c r="C139" s="10"/>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D139" s="10"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="9"/>
       <c r="B140" s="9"/>
       <c r="C140" s="10"/>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D140" s="10"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="9"/>
       <c r="B141" s="9"/>
       <c r="C141" s="10"/>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D141" s="10"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="9"/>
       <c r="B142" s="9"/>
       <c r="C142" s="10"/>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D142" s="10"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="9"/>
       <c r="B143" s="9"/>
       <c r="C143" s="10"/>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D143" s="10"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="9"/>
       <c r="B144" s="9"/>
       <c r="C144" s="10"/>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D144" s="10"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="9"/>
       <c r="B145" s="9"/>
       <c r="C145" s="10"/>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D145" s="10"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="9"/>
       <c r="B146" s="9"/>
       <c r="C146" s="10"/>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D146" s="10"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
       <c r="C147" s="10"/>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D147" s="10"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="9"/>
       <c r="B148" s="9"/>
       <c r="C148" s="10"/>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D148" s="10"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="9"/>
       <c r="B149" s="9"/>
       <c r="C149" s="10"/>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D149" s="10"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
       <c r="C150" s="10"/>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D150" s="10"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
       <c r="C151" s="10"/>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D151" s="10"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
       <c r="C152" s="10"/>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D152" s="10"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="9"/>
       <c r="B153" s="9"/>
       <c r="C153" s="10"/>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D153" s="10"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="9"/>
       <c r="B154" s="9"/>
       <c r="C154" s="10"/>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D154" s="10"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
       <c r="C155" s="10"/>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D155" s="10"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" s="9"/>
       <c r="B156" s="9"/>
       <c r="C156" s="10"/>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D156" s="10"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" s="9"/>
       <c r="B157" s="9"/>
       <c r="C157" s="10"/>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D157" s="10"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" s="9"/>
       <c r="B158" s="9"/>
       <c r="C158" s="10"/>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D158" s="10"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" s="9"/>
       <c r="B159" s="9"/>
       <c r="C159" s="10"/>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D159" s="10"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" s="9"/>
       <c r="B160" s="9"/>
       <c r="C160" s="10"/>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D160" s="10"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" s="9"/>
       <c r="B161" s="9"/>
       <c r="C161" s="10"/>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D161" s="10"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" s="9"/>
       <c r="B162" s="9"/>
       <c r="C162" s="10"/>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D162" s="10"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" s="9"/>
       <c r="B163" s="9"/>
       <c r="C163" s="10"/>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D163" s="10"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" s="9"/>
       <c r="B164" s="9"/>
       <c r="C164" s="10"/>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D164" s="10"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" s="9"/>
       <c r="B165" s="9"/>
       <c r="C165" s="10"/>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D165" s="10"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" s="9"/>
       <c r="B166" s="9"/>
       <c r="C166" s="10"/>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D166" s="10"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" s="9"/>
       <c r="B167" s="9"/>
       <c r="C167" s="10"/>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D167" s="10"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" s="9"/>
       <c r="B168" s="9"/>
       <c r="C168" s="10"/>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D168" s="10"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="C169" s="10"/>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D169" s="10"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" s="9"/>
       <c r="B170" s="9"/>
       <c r="C170" s="10"/>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D170" s="10"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" s="9"/>
       <c r="B171" s="9"/>
       <c r="C171" s="10"/>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D171" s="10"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" s="9"/>
       <c r="B172" s="9"/>
       <c r="C172" s="10"/>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D172" s="10"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" s="9"/>
       <c r="B173" s="9"/>
       <c r="C173" s="10"/>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D173" s="10"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" s="9"/>
       <c r="B174" s="9"/>
       <c r="C174" s="10"/>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D174" s="10"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" s="9"/>
       <c r="B175" s="9"/>
       <c r="C175" s="10"/>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D175" s="10"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" s="9"/>
       <c r="B176" s="9"/>
       <c r="C176" s="10"/>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D176" s="10"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" s="9"/>
       <c r="B177" s="9"/>
       <c r="C177" s="10"/>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D177" s="10"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" s="9"/>
       <c r="B178" s="9"/>
       <c r="C178" s="10"/>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D178" s="10"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" s="9"/>
       <c r="B179" s="9"/>
       <c r="C179" s="10"/>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D179" s="10"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" s="9"/>
       <c r="B180" s="9"/>
       <c r="C180" s="10"/>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D180" s="10"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" s="9"/>
       <c r="B181" s="9"/>
       <c r="C181" s="10"/>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D181" s="10"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" s="9"/>
       <c r="B182" s="9"/>
       <c r="C182" s="10"/>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D182" s="10"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" s="9"/>
       <c r="B183" s="9"/>
       <c r="C183" s="10"/>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D183" s="10"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" s="9"/>
       <c r="B184" s="9"/>
       <c r="C184" s="10"/>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D184" s="10"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" s="9"/>
       <c r="B185" s="9"/>
       <c r="C185" s="10"/>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D185" s="10"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" s="9"/>
       <c r="B186" s="9"/>
       <c r="C186" s="10"/>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D186" s="10"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" s="9"/>
       <c r="B187" s="9"/>
       <c r="C187" s="10"/>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D187" s="10"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="C188" s="10"/>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D188" s="10"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" s="9"/>
       <c r="B189" s="9"/>
       <c r="C189" s="10"/>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D189" s="10"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" s="9"/>
       <c r="B190" s="9"/>
       <c r="C190" s="10"/>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D190" s="10"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10"/>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D191" s="10"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="10"/>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D192" s="10"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D193" s="10"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D194" s="10"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D195" s="10"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" s="9"/>
       <c r="B196" s="9"/>
       <c r="C196" s="10"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D196" s="10"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" s="9"/>
       <c r="B197" s="9"/>
       <c r="C197" s="10"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D197" s="10"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" s="9"/>
       <c r="B198" s="9"/>
       <c r="C198" s="10"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D198" s="10"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" s="9"/>
       <c r="B199" s="9"/>
       <c r="C199" s="10"/>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D199" s="10"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10"/>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D200" s="10"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10"/>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D201" s="10"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10"/>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D202" s="10"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D203" s="10"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204" s="9"/>
       <c r="B204" s="9"/>
       <c r="C204" s="10"/>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D204" s="10"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" s="9"/>
       <c r="B205" s="9"/>
       <c r="C205" s="10"/>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D205" s="10"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206" s="9"/>
       <c r="B206" s="9"/>
       <c r="C206" s="10"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D206" s="10"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" s="9"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D207" s="9"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" s="9"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D208" s="9"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="9"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
+      <c r="D209" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
